--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_2048_run5/epoch_90/per_file_predictions_epoch_90.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_2048_run5/epoch_90/per_file_predictions_epoch_90.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="520">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="524">
   <si>
     <t>Filename</t>
   </si>
@@ -808,772 +808,784 @@
     <t>0,1,1,0</t>
   </si>
   <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
     <t>0,1,0,1</t>
   </si>
   <si>
-    <t>0.9360,0.0242,0.0114,0.0199</t>
-  </si>
-  <si>
-    <t>0.0066,0.0038,0.0012,0.9951</t>
-  </si>
-  <si>
-    <t>0.9037,0.0013,0.0009,0.1435</t>
-  </si>
-  <si>
-    <t>0.1820,0.0007,0.0003,0.9506</t>
-  </si>
-  <si>
-    <t>0.9975,0.0005,0.0003,0.0005</t>
-  </si>
-  <si>
-    <t>0.9946,0.0009,0.0001,0.0020</t>
-  </si>
-  <si>
-    <t>0.9919,0.0015,0.0015,0.0018</t>
-  </si>
-  <si>
-    <t>0.9928,0.0008,0.0004,0.0031</t>
-  </si>
-  <si>
-    <t>0.9666,0.0377,0.0017,0.0025</t>
-  </si>
-  <si>
-    <t>0.9860,0.0069,0.0022,0.0024</t>
-  </si>
-  <si>
-    <t>0.9964,0.0005,0.0002,0.0009</t>
-  </si>
-  <si>
-    <t>0.9963,0.0008,0.0008,0.0006</t>
-  </si>
-  <si>
-    <t>0.8131,0.0120,0.2483,0.0067</t>
-  </si>
-  <si>
-    <t>0.0044,0.0155,0.9793,0.0068</t>
-  </si>
-  <si>
-    <t>0.1593,0.0100,0.8847,0.0005</t>
-  </si>
-  <si>
-    <t>0.0949,0.0089,0.9238,0.0009</t>
-  </si>
-  <si>
-    <t>0.9804,0.0046,0.0106,0.0009</t>
-  </si>
-  <si>
-    <t>0.0007,0.9980,0.0018,0.0001</t>
-  </si>
-  <si>
-    <t>0.0011,0.9959,0.0024,0.0023</t>
-  </si>
-  <si>
-    <t>0.2255,0.8560,0.0028,0.0009</t>
-  </si>
-  <si>
-    <t>0.0017,0.9929,0.0065,0.0022</t>
-  </si>
-  <si>
-    <t>0.0043,0.9876,0.0058,0.0034</t>
-  </si>
-  <si>
-    <t>0.7204,0.0026,0.4016,0.0041</t>
-  </si>
-  <si>
-    <t>0.8779,0.0074,0.1419,0.0088</t>
-  </si>
-  <si>
-    <t>0.0010,0.0009,0.9953,0.0013</t>
-  </si>
-  <si>
-    <t>0.2001,0.0178,0.8096,0.0062</t>
-  </si>
-  <si>
-    <t>0.1178,0.0025,0.9413,0.0008</t>
-  </si>
-  <si>
-    <t>0.0119,0.0027,0.9743,0.0100</t>
-  </si>
-  <si>
-    <t>0.0010,0.0003,0.9971,0.0011</t>
-  </si>
-  <si>
-    <t>0.3581,0.6833,0.0171,0.0010</t>
-  </si>
-  <si>
-    <t>0.8464,0.1173,0.0487,0.0074</t>
-  </si>
-  <si>
-    <t>0.0001,0.0026,0.9976,0.0037</t>
-  </si>
-  <si>
-    <t>0.0079,0.9760,0.0253,0.0008</t>
-  </si>
-  <si>
-    <t>0.9789,0.0164,0.0009,0.0016</t>
-  </si>
-  <si>
-    <t>0.9494,0.0067,0.0388,0.0054</t>
-  </si>
-  <si>
-    <t>0.2041,0.8234,0.0043,0.0080</t>
-  </si>
-  <si>
-    <t>0.0019,0.9883,0.0129,0.0057</t>
-  </si>
-  <si>
-    <t>0.0492,0.0269,0.9145,0.0136</t>
-  </si>
-  <si>
-    <t>0.0299,0.0181,0.9629,0.0067</t>
-  </si>
-  <si>
-    <t>0.0433,0.1164,0.9065,0.0380</t>
-  </si>
-  <si>
-    <t>0.0044,0.0014,0.9897,0.0042</t>
-  </si>
-  <si>
-    <t>0.0014,0.6246,0.9813,0.0006</t>
-  </si>
-  <si>
-    <t>0.0016,0.9879,0.0086,0.0005</t>
-  </si>
-  <si>
-    <t>0.0031,0.0046,0.9914,0.0014</t>
-  </si>
-  <si>
-    <t>0.0297,0.7666,0.0103,0.6366</t>
-  </si>
-  <si>
-    <t>0.0061,0.9866,0.0039,0.0020</t>
-  </si>
-  <si>
-    <t>0.0007,0.9846,0.1802,0.0019</t>
-  </si>
-  <si>
-    <t>0.0007,0.9903,0.0102,0.0037</t>
-  </si>
-  <si>
-    <t>0.0036,0.0032,0.9933,0.0010</t>
-  </si>
-  <si>
-    <t>0.0002,0.0542,0.9968,0.0002</t>
-  </si>
-  <si>
-    <t>0.0591,0.0265,0.9268,0.0161</t>
-  </si>
-  <si>
-    <t>0.0126,0.0025,0.9848,0.0032</t>
-  </si>
-  <si>
-    <t>0.0040,0.0109,0.9893,0.0015</t>
-  </si>
-  <si>
-    <t>0.0135,0.1499,0.9508,0.0017</t>
-  </si>
-  <si>
-    <t>0.9839,0.0157,0.0012,0.0008</t>
-  </si>
-  <si>
-    <t>0.9934,0.0013,0.0013,0.0013</t>
-  </si>
-  <si>
-    <t>0.9938,0.0011,0.0008,0.0019</t>
-  </si>
-  <si>
-    <t>0.0007,0.0100,0.9934,0.0054</t>
-  </si>
-  <si>
-    <t>0.9893,0.0036,0.0015,0.0017</t>
-  </si>
-  <si>
-    <t>0.9952,0.0020,0.0010,0.0004</t>
-  </si>
-  <si>
-    <t>0.9877,0.0079,0.0010,0.0020</t>
-  </si>
-  <si>
-    <t>0.0003,0.9474,0.9746,0.0005</t>
-  </si>
-  <si>
-    <t>0.0041,0.0211,0.9927,0.0016</t>
-  </si>
-  <si>
-    <t>0.0010,0.0249,0.9883,0.0102</t>
-  </si>
-  <si>
-    <t>0.0017,0.8438,0.8955,0.0028</t>
-  </si>
-  <si>
-    <t>0.0026,0.0021,0.9958,0.0010</t>
-  </si>
-  <si>
-    <t>0.4592,0.7217,0.0016,0.0003</t>
-  </si>
-  <si>
-    <t>0.0009,0.9983,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.8187,0.0109,0.2807,0.0038</t>
-  </si>
-  <si>
-    <t>0.0918,0.0456,0.9096,0.0020</t>
-  </si>
-  <si>
-    <t>0.0032,0.0089,0.9939,0.0004</t>
-  </si>
-  <si>
-    <t>0.0002,0.9870,0.9161,0.0001</t>
-  </si>
-  <si>
-    <t>0.0012,0.9444,0.8349,0.0004</t>
-  </si>
-  <si>
-    <t>0.0001,0.9994,0.0027,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9959,0.9145,0.0000</t>
-  </si>
-  <si>
-    <t>0.0187,0.0044,0.0412,0.9705</t>
-  </si>
-  <si>
-    <t>0.0028,0.0005,0.0001,0.9987</t>
-  </si>
-  <si>
-    <t>0.0041,0.0056,0.0015,0.9965</t>
-  </si>
-  <si>
-    <t>0.0035,0.0016,0.0011,0.9970</t>
-  </si>
-  <si>
-    <t>0.0007,0.0019,0.0013,0.9986</t>
-  </si>
-  <si>
-    <t>0.0049,0.0096,0.0015,0.9956</t>
-  </si>
-  <si>
-    <t>0.0001,0.9919,0.9682,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.8438,0.9942,0.0001</t>
-  </si>
-  <si>
-    <t>0.0026,0.9834,0.0182,0.0012</t>
-  </si>
-  <si>
-    <t>0.0001,0.8934,0.9941,0.0003</t>
-  </si>
-  <si>
-    <t>0.0013,0.9412,0.8485,0.0004</t>
-  </si>
-  <si>
-    <t>0.0008,0.9826,0.3962,0.0002</t>
-  </si>
-  <si>
-    <t>0.9970,0.0008,0.0005,0.0004</t>
-  </si>
-  <si>
-    <t>0.9955,0.0035,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9850,0.0175,0.0012,0.0009</t>
-  </si>
-  <si>
-    <t>0.9955,0.0014,0.0003,0.0010</t>
-  </si>
-  <si>
-    <t>0.9890,0.0132,0.0011,0.0005</t>
-  </si>
-  <si>
-    <t>0.9945,0.0022,0.0006,0.0007</t>
-  </si>
-  <si>
-    <t>0.9651,0.0345,0.0087,0.0008</t>
-  </si>
-  <si>
-    <t>0.9795,0.0195,0.0054,0.0005</t>
-  </si>
-  <si>
-    <t>0.9953,0.0004,0.0003,0.0020</t>
-  </si>
-  <si>
-    <t>0.9986,0.0004,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.9965,0.0005,0.0003,0.0009</t>
-  </si>
-  <si>
-    <t>0.9977,0.0001,0.0003,0.0009</t>
-  </si>
-  <si>
-    <t>0.9971,0.0002,0.0001,0.0014</t>
-  </si>
-  <si>
-    <t>0.9907,0.0031,0.0038,0.0010</t>
-  </si>
-  <si>
-    <t>0.9969,0.0003,0.0006,0.0009</t>
-  </si>
-  <si>
-    <t>0.9925,0.0013,0.0011,0.0018</t>
-  </si>
-  <si>
-    <t>0.0014,0.0001,0.9976,0.0006</t>
-  </si>
-  <si>
-    <t>0.0052,0.0055,0.9867,0.0022</t>
-  </si>
-  <si>
-    <t>0.9561,0.0019,0.0196,0.0094</t>
-  </si>
-  <si>
-    <t>0.0219,0.0032,0.9804,0.0011</t>
-  </si>
-  <si>
-    <t>0.0046,0.9893,0.0053,0.0008</t>
-  </si>
-  <si>
-    <t>0.0039,0.9906,0.0031,0.0018</t>
-  </si>
-  <si>
-    <t>0.0513,0.9494,0.0083,0.0038</t>
-  </si>
-  <si>
-    <t>0.0635,0.9321,0.0136,0.0092</t>
-  </si>
-  <si>
-    <t>0.0007,0.9962,0.0096,0.0011</t>
-  </si>
-  <si>
-    <t>0.0014,0.9955,0.0098,0.0006</t>
-  </si>
-  <si>
-    <t>0.4624,0.6891,0.0021,0.0012</t>
-  </si>
-  <si>
-    <t>0.7823,0.0598,0.2031,0.0086</t>
-  </si>
-  <si>
-    <t>0.1193,0.0544,0.8444,0.0286</t>
-  </si>
-  <si>
-    <t>0.4723,0.0303,0.5008,0.0143</t>
-  </si>
-  <si>
-    <t>0.4236,0.0070,0.7412,0.0016</t>
-  </si>
-  <si>
-    <t>0.0884,0.0382,0.0659,0.8963</t>
-  </si>
-  <si>
-    <t>0.0002,0.9988,0.0048,0.0001</t>
-  </si>
-  <si>
-    <t>0.0012,0.9950,0.0019,0.0007</t>
-  </si>
-  <si>
-    <t>0.0000,0.9995,0.0011,0.0030</t>
-  </si>
-  <si>
-    <t>0.0006,0.8621,0.6705,0.0137</t>
-  </si>
-  <si>
-    <t>0.0074,0.9835,0.0075,0.0030</t>
-  </si>
-  <si>
-    <t>0.4211,0.6300,0.0347,0.0080</t>
-  </si>
-  <si>
-    <t>0.8003,0.2698,0.0092,0.0059</t>
-  </si>
-  <si>
-    <t>0.9964,0.0007,0.0001,0.0010</t>
-  </si>
-  <si>
-    <t>0.9912,0.0014,0.0033,0.0017</t>
-  </si>
-  <si>
-    <t>0.9941,0.0008,0.0005,0.0017</t>
-  </si>
-  <si>
-    <t>0.9959,0.0010,0.0007,0.0005</t>
-  </si>
-  <si>
-    <t>0.9986,0.0002,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9935,0.0020,0.0005,0.0013</t>
-  </si>
-  <si>
-    <t>0.9934,0.0003,0.0005,0.0034</t>
-  </si>
-  <si>
-    <t>0.9819,0.0009,0.0142,0.0018</t>
-  </si>
-  <si>
-    <t>0.0087,0.8416,0.7489,0.0030</t>
-  </si>
-  <si>
-    <t>0.0006,0.9833,0.6419,0.0002</t>
-  </si>
-  <si>
-    <t>0.0139,0.0498,0.9530,0.0014</t>
-  </si>
-  <si>
-    <t>0.1207,0.0673,0.8614,0.0017</t>
-  </si>
-  <si>
-    <t>0.9940,0.0012,0.0017,0.0004</t>
-  </si>
-  <si>
-    <t>0.5216,0.0108,0.6320,0.0008</t>
-  </si>
-  <si>
-    <t>0.2139,0.0009,0.8936,0.0027</t>
-  </si>
-  <si>
-    <t>0.5948,0.0329,0.4518,0.0110</t>
-  </si>
-  <si>
-    <t>0.3522,0.0035,0.0021,0.8516</t>
-  </si>
-  <si>
-    <t>0.0000,0.0002,0.0053,0.9992</t>
-  </si>
-  <si>
-    <t>0.0001,0.0026,0.0004,0.9996</t>
-  </si>
-  <si>
-    <t>0.0061,0.0005,0.0005,0.9964</t>
-  </si>
-  <si>
-    <t>0.0005,0.8570,0.7719,0.0010</t>
-  </si>
-  <si>
-    <t>0.9892,0.0030,0.0010,0.0021</t>
-  </si>
-  <si>
-    <t>0.0322,0.9670,0.0030,0.0058</t>
-  </si>
-  <si>
-    <t>0.9906,0.0032,0.0024,0.0011</t>
-  </si>
-  <si>
-    <t>0.0683,0.9389,0.0106,0.0054</t>
-  </si>
-  <si>
-    <t>0.9859,0.0012,0.0035,0.0053</t>
-  </si>
-  <si>
-    <t>0.8847,0.0091,0.0032,0.1074</t>
-  </si>
-  <si>
-    <t>0.9916,0.0031,0.0018,0.0015</t>
-  </si>
-  <si>
-    <t>0.0013,0.0053,0.9085,0.3776</t>
-  </si>
-  <si>
-    <t>0.9120,0.0003,0.0002,0.2188</t>
-  </si>
-  <si>
-    <t>0.9478,0.0014,0.0015,0.0570</t>
-  </si>
-  <si>
-    <t>0.3254,0.7232,0.0093,0.0148</t>
-  </si>
-  <si>
-    <t>0.9873,0.0061,0.0032,0.0006</t>
-  </si>
-  <si>
-    <t>0.9822,0.0062,0.0087,0.0011</t>
-  </si>
-  <si>
-    <t>0.0584,0.9059,0.0377,0.0121</t>
-  </si>
-  <si>
-    <t>0.8655,0.0352,0.0946,0.0010</t>
-  </si>
-  <si>
-    <t>0.9468,0.0489,0.0095,0.0015</t>
-  </si>
-  <si>
-    <t>0.9951,0.0012,0.0016,0.0007</t>
-  </si>
-  <si>
-    <t>0.9905,0.0016,0.0008,0.0034</t>
-  </si>
-  <si>
-    <t>0.9941,0.0009,0.0007,0.0015</t>
-  </si>
-  <si>
-    <t>0.9873,0.0007,0.0041,0.0038</t>
-  </si>
-  <si>
-    <t>0.9957,0.0005,0.0004,0.0011</t>
-  </si>
-  <si>
-    <t>0.9753,0.0077,0.0130,0.0031</t>
-  </si>
-  <si>
-    <t>0.9958,0.0003,0.0003,0.0019</t>
-  </si>
-  <si>
-    <t>0.9893,0.0008,0.0009,0.0052</t>
-  </si>
-  <si>
-    <t>0.6938,0.2257,0.0043,0.0193</t>
-  </si>
-  <si>
-    <t>0.5122,0.5584,0.0044,0.0039</t>
-  </si>
-  <si>
-    <t>0.6486,0.4807,0.0013,0.0019</t>
-  </si>
-  <si>
-    <t>0.4863,0.1018,0.5317,0.0147</t>
-  </si>
-  <si>
-    <t>0.9834,0.0143,0.0021,0.0007</t>
-  </si>
-  <si>
-    <t>0.9752,0.0209,0.0021,0.0026</t>
-  </si>
-  <si>
-    <t>0.9956,0.0013,0.0007,0.0007</t>
-  </si>
-  <si>
-    <t>0.9571,0.0381,0.0071,0.0022</t>
-  </si>
-  <si>
-    <t>0.0001,0.0021,0.9995,0.0002</t>
-  </si>
-  <si>
-    <t>0.9810,0.0108,0.0028,0.0021</t>
-  </si>
-  <si>
-    <t>0.0016,0.0035,0.9964,0.0001</t>
-  </si>
-  <si>
-    <t>0.0015,0.1434,0.9867,0.0022</t>
-  </si>
-  <si>
-    <t>0.0023,0.0038,0.9898,0.0052</t>
-  </si>
-  <si>
-    <t>0.0007,0.0521,0.9971,0.0002</t>
-  </si>
-  <si>
-    <t>0.0043,0.0035,0.9933,0.0002</t>
-  </si>
-  <si>
-    <t>0.0092,0.0026,0.9888,0.0004</t>
-  </si>
-  <si>
-    <t>0.0024,0.0086,0.9944,0.0004</t>
-  </si>
-  <si>
-    <t>0.1724,0.1555,0.7012,0.0471</t>
-  </si>
-  <si>
-    <t>0.0337,0.0089,0.9565,0.0033</t>
-  </si>
-  <si>
-    <t>0.3472,0.0930,0.5823,0.0103</t>
-  </si>
-  <si>
-    <t>0.7883,0.0834,0.0964,0.0029</t>
-  </si>
-  <si>
-    <t>0.1224,0.2092,0.5644,0.0016</t>
-  </si>
-  <si>
-    <t>0.3080,0.0567,0.6774,0.0032</t>
-  </si>
-  <si>
-    <t>0.8880,0.0190,0.1243,0.0044</t>
-  </si>
-  <si>
-    <t>0.3185,0.0127,0.7514,0.0094</t>
-  </si>
-  <si>
-    <t>0.6981,0.6050,0.0006,0.0002</t>
-  </si>
-  <si>
-    <t>0.2758,0.8592,0.0015,0.0006</t>
-  </si>
-  <si>
-    <t>0.9073,0.1642,0.0035,0.0006</t>
-  </si>
-  <si>
-    <t>0.4437,0.7116,0.0037,0.0032</t>
-  </si>
-  <si>
-    <t>0.1591,0.8981,0.0048,0.0023</t>
-  </si>
-  <si>
-    <t>0.8518,0.1000,0.0223,0.0060</t>
-  </si>
-  <si>
-    <t>0.9794,0.0094,0.0069,0.0011</t>
-  </si>
-  <si>
-    <t>0.9384,0.0039,0.0357,0.0099</t>
-  </si>
-  <si>
-    <t>0.9284,0.0228,0.0607,0.0018</t>
-  </si>
-  <si>
-    <t>0.8067,0.0036,0.1999,0.0136</t>
-  </si>
-  <si>
-    <t>0.0311,0.0029,0.9696,0.0030</t>
-  </si>
-  <si>
-    <t>0.0009,0.2747,0.9482,0.0021</t>
-  </si>
-  <si>
-    <t>0.0145,0.1919,0.9467,0.0076</t>
-  </si>
-  <si>
-    <t>0.0344,0.1063,0.9068,0.0083</t>
-  </si>
-  <si>
-    <t>0.0011,0.0201,0.9798,0.0116</t>
-  </si>
-  <si>
-    <t>0.9979,0.0004,0.0004,0.0003</t>
-  </si>
-  <si>
-    <t>0.9903,0.0025,0.0017,0.0020</t>
-  </si>
-  <si>
-    <t>0.9606,0.0352,0.0099,0.0030</t>
-  </si>
-  <si>
-    <t>0.8884,0.1677,0.0061,0.0023</t>
-  </si>
-  <si>
-    <t>0.9753,0.0192,0.0030,0.0029</t>
-  </si>
-  <si>
-    <t>0.8831,0.1638,0.0023,0.0040</t>
-  </si>
-  <si>
-    <t>0.9758,0.0075,0.0020,0.0077</t>
-  </si>
-  <si>
-    <t>0.9940,0.0006,0.0006,0.0022</t>
-  </si>
-  <si>
-    <t>0.0066,0.0073,0.9788,0.0076</t>
-  </si>
-  <si>
-    <t>0.0404,0.1288,0.8451,0.0279</t>
-  </si>
-  <si>
-    <t>0.9309,0.0037,0.0443,0.0090</t>
-  </si>
-  <si>
-    <t>0.0081,0.0010,0.9945,0.0001</t>
-  </si>
-  <si>
-    <t>0.0008,0.0011,0.9961,0.0020</t>
-  </si>
-  <si>
-    <t>0.0029,0.1523,0.9114,0.0009</t>
-  </si>
-  <si>
-    <t>0.0025,0.0060,0.9949,0.0006</t>
-  </si>
-  <si>
-    <t>0.0146,0.0250,0.9512,0.0068</t>
-  </si>
-  <si>
-    <t>0.0011,0.0059,0.9968,0.0007</t>
-  </si>
-  <si>
-    <t>0.0094,0.0038,0.9815,0.0082</t>
-  </si>
-  <si>
-    <t>0.0507,0.0076,0.9349,0.0072</t>
-  </si>
-  <si>
-    <t>0.9713,0.0042,0.0211,0.0022</t>
-  </si>
-  <si>
-    <t>0.8028,0.0010,0.3032,0.0029</t>
-  </si>
-  <si>
-    <t>0.9646,0.0098,0.0117,0.0031</t>
-  </si>
-  <si>
-    <t>0.9975,0.0011,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9896,0.0088,0.0012,0.0007</t>
-  </si>
-  <si>
-    <t>0.9969,0.0016,0.0005,0.0003</t>
-  </si>
-  <si>
-    <t>0.9868,0.0086,0.0016,0.0010</t>
-  </si>
-  <si>
-    <t>0.9870,0.0025,0.0021,0.0042</t>
-  </si>
-  <si>
-    <t>0.9850,0.0153,0.0019,0.0006</t>
-  </si>
-  <si>
-    <t>0.9927,0.0067,0.0006,0.0004</t>
-  </si>
-  <si>
-    <t>0.9884,0.0100,0.0008,0.0011</t>
-  </si>
-  <si>
-    <t>0.0122,0.0121,0.9705,0.0014</t>
-  </si>
-  <si>
-    <t>0.0112,0.0379,0.9793,0.0005</t>
-  </si>
-  <si>
-    <t>0.0024,0.0057,0.9889,0.0026</t>
-  </si>
-  <si>
-    <t>0.0109,0.0096,0.9760,0.0014</t>
-  </si>
-  <si>
-    <t>0.0002,0.0005,0.9981,0.0029</t>
-  </si>
-  <si>
-    <t>0.0147,0.0111,0.9631,0.0206</t>
-  </si>
-  <si>
-    <t>0.0030,0.0117,0.9858,0.0058</t>
-  </si>
-  <si>
-    <t>0.0178,0.0028,0.9468,0.0434</t>
-  </si>
-  <si>
-    <t>0.9897,0.0006,0.0003,0.0094</t>
-  </si>
-  <si>
-    <t>0.0103,0.0844,0.0055,0.9823</t>
-  </si>
-  <si>
-    <t>0.0573,0.0017,0.0102,0.9461</t>
-  </si>
-  <si>
-    <t>0.0138,0.0002,0.0017,0.9920</t>
-  </si>
-  <si>
-    <t>0.0031,0.0057,0.0011,0.9969</t>
-  </si>
-  <si>
-    <t>0.3843,0.0415,0.0070,0.6827</t>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>0,0,1,1</t>
+  </si>
+  <si>
+    <t>0.9254,0.0251,0.0185,0.0276</t>
+  </si>
+  <si>
+    <t>0.0083,0.0309,0.0006,0.9923</t>
+  </si>
+  <si>
+    <t>0.7467,0.0053,0.0050,0.3422</t>
+  </si>
+  <si>
+    <t>0.0892,0.0069,0.0011,0.9524</t>
+  </si>
+  <si>
+    <t>0.9974,0.0004,0.0005,0.0004</t>
+  </si>
+  <si>
+    <t>0.9935,0.0046,0.0003,0.0009</t>
+  </si>
+  <si>
+    <t>0.9934,0.0013,0.0021,0.0013</t>
+  </si>
+  <si>
+    <t>0.9941,0.0003,0.0004,0.0031</t>
+  </si>
+  <si>
+    <t>0.9794,0.0209,0.0005,0.0014</t>
+  </si>
+  <si>
+    <t>0.9877,0.0054,0.0005,0.0021</t>
+  </si>
+  <si>
+    <t>0.9956,0.0007,0.0008,0.0011</t>
+  </si>
+  <si>
+    <t>0.9960,0.0010,0.0004,0.0010</t>
+  </si>
+  <si>
+    <t>0.8982,0.0839,0.0189,0.0025</t>
+  </si>
+  <si>
+    <t>0.1469,0.3364,0.4534,0.0016</t>
+  </si>
+  <si>
+    <t>0.0597,0.0112,0.9490,0.0002</t>
+  </si>
+  <si>
+    <t>0.0316,0.0076,0.9733,0.0003</t>
+  </si>
+  <si>
+    <t>0.9886,0.0012,0.0196,0.0001</t>
+  </si>
+  <si>
+    <t>0.0007,0.9986,0.0008,0.0000</t>
+  </si>
+  <si>
+    <t>0.0020,0.9932,0.0052,0.0011</t>
+  </si>
+  <si>
+    <t>0.0439,0.9604,0.0018,0.0006</t>
+  </si>
+  <si>
+    <t>0.0185,0.9728,0.0072,0.0057</t>
+  </si>
+  <si>
+    <t>0.0021,0.9924,0.0149,0.0015</t>
+  </si>
+  <si>
+    <t>0.4004,0.0075,0.6272,0.0247</t>
+  </si>
+  <si>
+    <t>0.8937,0.0132,0.0899,0.0122</t>
+  </si>
+  <si>
+    <t>0.0034,0.0037,0.9913,0.0007</t>
+  </si>
+  <si>
+    <t>0.0161,0.0077,0.9700,0.0020</t>
+  </si>
+  <si>
+    <t>0.0094,0.0020,0.9889,0.0008</t>
+  </si>
+  <si>
+    <t>0.1307,0.0034,0.7063,0.1059</t>
+  </si>
+  <si>
+    <t>0.0012,0.0010,0.9951,0.0023</t>
+  </si>
+  <si>
+    <t>0.5640,0.5538,0.0073,0.0014</t>
+  </si>
+  <si>
+    <t>0.1043,0.1611,0.7569,0.0026</t>
+  </si>
+  <si>
+    <t>0.0004,0.0024,0.9964,0.0036</t>
+  </si>
+  <si>
+    <t>0.0863,0.9248,0.0046,0.0004</t>
+  </si>
+  <si>
+    <t>0.9611,0.0229,0.0044,0.0042</t>
+  </si>
+  <si>
+    <t>0.3640,0.0067,0.6734,0.0103</t>
+  </si>
+  <si>
+    <t>0.8350,0.2263,0.0044,0.0024</t>
+  </si>
+  <si>
+    <t>0.0083,0.9740,0.1139,0.0063</t>
+  </si>
+  <si>
+    <t>0.0201,0.2733,0.6792,0.0096</t>
+  </si>
+  <si>
+    <t>0.0106,0.0006,0.9827,0.0043</t>
+  </si>
+  <si>
+    <t>0.0019,0.0146,0.9805,0.0325</t>
+  </si>
+  <si>
+    <t>0.0025,0.0027,0.9927,0.0043</t>
+  </si>
+  <si>
+    <t>0.0040,0.0150,0.9860,0.0020</t>
+  </si>
+  <si>
+    <t>0.0049,0.9604,0.0230,0.0029</t>
+  </si>
+  <si>
+    <t>0.0013,0.0052,0.9929,0.0016</t>
+  </si>
+  <si>
+    <t>0.0865,0.6311,0.0928,0.5409</t>
+  </si>
+  <si>
+    <t>0.0069,0.9638,0.0038,0.0596</t>
+  </si>
+  <si>
+    <t>0.0005,0.9957,0.0039,0.0017</t>
+  </si>
+  <si>
+    <t>0.0005,0.9907,0.0316,0.0054</t>
+  </si>
+  <si>
+    <t>0.0010,0.0074,0.9932,0.0011</t>
+  </si>
+  <si>
+    <t>0.0000,0.1636,0.9980,0.0002</t>
+  </si>
+  <si>
+    <t>0.0013,0.0008,0.9956,0.0016</t>
+  </si>
+  <si>
+    <t>0.0108,0.0007,0.9855,0.0049</t>
+  </si>
+  <si>
+    <t>0.0007,0.0025,0.9936,0.0040</t>
+  </si>
+  <si>
+    <t>0.0015,0.0371,0.9822,0.0015</t>
+  </si>
+  <si>
+    <t>0.9806,0.0082,0.0003,0.0026</t>
+  </si>
+  <si>
+    <t>0.9974,0.0006,0.0004,0.0004</t>
+  </si>
+  <si>
+    <t>0.9848,0.0035,0.0175,0.0006</t>
+  </si>
+  <si>
+    <t>0.0016,0.0052,0.9943,0.0024</t>
+  </si>
+  <si>
+    <t>0.9839,0.0067,0.0074,0.0021</t>
+  </si>
+  <si>
+    <t>0.9953,0.0024,0.0007,0.0005</t>
+  </si>
+  <si>
+    <t>0.9962,0.0019,0.0007,0.0002</t>
+  </si>
+  <si>
+    <t>0.0006,0.9046,0.9763,0.0007</t>
+  </si>
+  <si>
+    <t>0.0002,0.0063,0.9983,0.0009</t>
+  </si>
+  <si>
+    <t>0.0008,0.0017,0.9964,0.0031</t>
+  </si>
+  <si>
+    <t>0.0001,0.9580,0.9938,0.0001</t>
+  </si>
+  <si>
+    <t>0.0005,0.0003,0.9979,0.0009</t>
+  </si>
+  <si>
+    <t>0.1041,0.9227,0.0026,0.0005</t>
+  </si>
+  <si>
+    <t>0.0009,0.9987,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9957,0.0009,0.0014,0.0004</t>
+  </si>
+  <si>
+    <t>0.7334,0.0679,0.1971,0.0081</t>
+  </si>
+  <si>
+    <t>0.0013,0.0025,0.9959,0.0010</t>
+  </si>
+  <si>
+    <t>0.0001,0.9858,0.9288,0.0001</t>
+  </si>
+  <si>
+    <t>0.0009,0.9340,0.9204,0.0005</t>
+  </si>
+  <si>
+    <t>0.0007,0.9953,0.0294,0.0005</t>
+  </si>
+  <si>
+    <t>0.0008,0.9890,0.3352,0.0003</t>
+  </si>
+  <si>
+    <t>0.0215,0.0016,0.0415,0.9628</t>
+  </si>
+  <si>
+    <t>0.0049,0.0015,0.0009,0.9965</t>
+  </si>
+  <si>
+    <t>0.0072,0.0078,0.0030,0.9941</t>
+  </si>
+  <si>
+    <t>0.0271,0.0006,0.0022,0.9862</t>
+  </si>
+  <si>
+    <t>0.0031,0.0004,0.0010,0.9976</t>
+  </si>
+  <si>
+    <t>0.0002,0.0042,0.0106,0.9972</t>
+  </si>
+  <si>
+    <t>0.0001,0.9917,0.9829,0.0001</t>
+  </si>
+  <si>
+    <t>0.0008,0.7415,0.9881,0.0004</t>
+  </si>
+  <si>
+    <t>0.0010,0.9596,0.5465,0.0007</t>
+  </si>
+  <si>
+    <t>0.0065,0.9341,0.5500,0.0105</t>
+  </si>
+  <si>
+    <t>0.0007,0.9864,0.4510,0.0003</t>
+  </si>
+  <si>
+    <t>0.0011,0.9750,0.4556,0.0003</t>
+  </si>
+  <si>
+    <t>0.9952,0.0010,0.0004,0.0011</t>
+  </si>
+  <si>
+    <t>0.9965,0.0022,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9903,0.0064,0.0014,0.0006</t>
+  </si>
+  <si>
+    <t>0.9958,0.0013,0.0002,0.0006</t>
+  </si>
+  <si>
+    <t>0.9904,0.0078,0.0010,0.0009</t>
+  </si>
+  <si>
+    <t>0.9958,0.0007,0.0002,0.0013</t>
+  </si>
+  <si>
+    <t>0.9869,0.0075,0.0022,0.0014</t>
+  </si>
+  <si>
+    <t>0.9911,0.0039,0.0021,0.0010</t>
+  </si>
+  <si>
+    <t>0.9977,0.0002,0.0002,0.0007</t>
+  </si>
+  <si>
+    <t>0.9980,0.0006,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.9906,0.0012,0.0011,0.0044</t>
+  </si>
+  <si>
+    <t>0.9986,0.0001,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9974,0.0003,0.0004,0.0008</t>
+  </si>
+  <si>
+    <t>0.9924,0.0031,0.0017,0.0011</t>
+  </si>
+  <si>
+    <t>0.9965,0.0005,0.0004,0.0012</t>
+  </si>
+  <si>
+    <t>0.9954,0.0002,0.0001,0.0026</t>
+  </si>
+  <si>
+    <t>0.0021,0.0005,0.9964,0.0013</t>
+  </si>
+  <si>
+    <t>0.0062,0.0150,0.9726,0.0130</t>
+  </si>
+  <si>
+    <t>0.9370,0.0087,0.0271,0.0077</t>
+  </si>
+  <si>
+    <t>0.0035,0.0045,0.9879,0.0022</t>
+  </si>
+  <si>
+    <t>0.0040,0.9836,0.0129,0.0074</t>
+  </si>
+  <si>
+    <t>0.0008,0.9968,0.0015,0.0011</t>
+  </si>
+  <si>
+    <t>0.0084,0.9809,0.0301,0.0011</t>
+  </si>
+  <si>
+    <t>0.0163,0.9767,0.0056,0.0024</t>
+  </si>
+  <si>
+    <t>0.0046,0.9884,0.0086,0.0018</t>
+  </si>
+  <si>
+    <t>0.0005,0.9979,0.0039,0.0002</t>
+  </si>
+  <si>
+    <t>0.6839,0.5097,0.0024,0.0006</t>
+  </si>
+  <si>
+    <t>0.7258,0.0033,0.4084,0.0036</t>
+  </si>
+  <si>
+    <t>0.7761,0.0066,0.3637,0.0019</t>
+  </si>
+  <si>
+    <t>0.6762,0.0200,0.3255,0.0092</t>
+  </si>
+  <si>
+    <t>0.6003,0.0154,0.5169,0.0042</t>
+  </si>
+  <si>
+    <t>0.0246,0.3674,0.0263,0.7786</t>
+  </si>
+  <si>
+    <t>0.0013,0.9949,0.0055,0.0003</t>
+  </si>
+  <si>
+    <t>0.0011,0.9950,0.0042,0.0010</t>
+  </si>
+  <si>
+    <t>0.0002,0.9955,0.0019,0.0448</t>
+  </si>
+  <si>
+    <t>0.0012,0.9508,0.6606,0.0075</t>
+  </si>
+  <si>
+    <t>0.0054,0.9838,0.0014,0.0029</t>
+  </si>
+  <si>
+    <t>0.5737,0.3761,0.1131,0.0061</t>
+  </si>
+  <si>
+    <t>0.8506,0.1878,0.0067,0.0029</t>
+  </si>
+  <si>
+    <t>0.9953,0.0024,0.0002,0.0008</t>
+  </si>
+  <si>
+    <t>0.9933,0.0003,0.0009,0.0032</t>
+  </si>
+  <si>
+    <t>0.9906,0.0030,0.0037,0.0008</t>
+  </si>
+  <si>
+    <t>0.9925,0.0014,0.0021,0.0013</t>
+  </si>
+  <si>
+    <t>0.9932,0.0006,0.0003,0.0032</t>
+  </si>
+  <si>
+    <t>0.9919,0.0040,0.0008,0.0015</t>
+  </si>
+  <si>
+    <t>0.9942,0.0004,0.0005,0.0024</t>
+  </si>
+  <si>
+    <t>0.9748,0.0069,0.0201,0.0017</t>
+  </si>
+  <si>
+    <t>0.0002,0.9829,0.9104,0.0005</t>
+  </si>
+  <si>
+    <t>0.0002,0.8281,0.9927,0.0001</t>
+  </si>
+  <si>
+    <t>0.0036,0.0656,0.9832,0.0008</t>
+  </si>
+  <si>
+    <t>0.0355,0.1265,0.9242,0.0021</t>
+  </si>
+  <si>
+    <t>0.9656,0.0114,0.0112,0.0040</t>
+  </si>
+  <si>
+    <t>0.9152,0.0178,0.0675,0.0018</t>
+  </si>
+  <si>
+    <t>0.1129,0.0024,0.8939,0.0107</t>
+  </si>
+  <si>
+    <t>0.8043,0.0125,0.1566,0.0217</t>
+  </si>
+  <si>
+    <t>0.1045,0.0013,0.0037,0.9548</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.0020,0.9995</t>
+  </si>
+  <si>
+    <t>0.0004,0.0014,0.0017,0.9989</t>
+  </si>
+  <si>
+    <t>0.0082,0.0002,0.0015,0.9943</t>
+  </si>
+  <si>
+    <t>0.0003,0.9747,0.6550,0.0004</t>
+  </si>
+  <si>
+    <t>0.9874,0.0023,0.0046,0.0018</t>
+  </si>
+  <si>
+    <t>0.0206,0.9757,0.0020,0.0037</t>
+  </si>
+  <si>
+    <t>0.9825,0.0042,0.0042,0.0025</t>
+  </si>
+  <si>
+    <t>0.1551,0.8948,0.0062,0.0025</t>
+  </si>
+  <si>
+    <t>0.9911,0.0007,0.0023,0.0028</t>
+  </si>
+  <si>
+    <t>0.7888,0.0155,0.0037,0.2296</t>
+  </si>
+  <si>
+    <t>0.9915,0.0019,0.0015,0.0023</t>
+  </si>
+  <si>
+    <t>0.0005,0.0025,0.8774,0.6390</t>
+  </si>
+  <si>
+    <t>0.9064,0.0007,0.0009,0.1497</t>
+  </si>
+  <si>
+    <t>0.9536,0.0040,0.0204,0.0134</t>
+  </si>
+  <si>
+    <t>0.6583,0.2684,0.0663,0.0122</t>
+  </si>
+  <si>
+    <t>0.9815,0.0054,0.0035,0.0028</t>
+  </si>
+  <si>
+    <t>0.9811,0.0070,0.0067,0.0011</t>
+  </si>
+  <si>
+    <t>0.0298,0.9445,0.0152,0.0120</t>
+  </si>
+  <si>
+    <t>0.7766,0.0473,0.1911,0.0012</t>
+  </si>
+  <si>
+    <t>0.9917,0.0034,0.0017,0.0005</t>
+  </si>
+  <si>
+    <t>0.9935,0.0008,0.0017,0.0015</t>
+  </si>
+  <si>
+    <t>0.9896,0.0021,0.0009,0.0032</t>
+  </si>
+  <si>
+    <t>0.9912,0.0025,0.0016,0.0016</t>
+  </si>
+  <si>
+    <t>0.9870,0.0011,0.0066,0.0026</t>
+  </si>
+  <si>
+    <t>0.9899,0.0038,0.0008,0.0020</t>
+  </si>
+  <si>
+    <t>0.9740,0.0148,0.0091,0.0036</t>
+  </si>
+  <si>
+    <t>0.9955,0.0007,0.0004,0.0015</t>
+  </si>
+  <si>
+    <t>0.9937,0.0003,0.0006,0.0027</t>
+  </si>
+  <si>
+    <t>0.8792,0.1074,0.0004,0.0041</t>
+  </si>
+  <si>
+    <t>0.7336,0.3750,0.0026,0.0029</t>
+  </si>
+  <si>
+    <t>0.8846,0.1505,0.0035,0.0041</t>
+  </si>
+  <si>
+    <t>0.8984,0.0690,0.0449,0.0105</t>
+  </si>
+  <si>
+    <t>0.9801,0.0212,0.0007,0.0007</t>
+  </si>
+  <si>
+    <t>0.9942,0.0011,0.0007,0.0013</t>
+  </si>
+  <si>
+    <t>0.9955,0.0010,0.0003,0.0009</t>
+  </si>
+  <si>
+    <t>0.9590,0.0219,0.0116,0.0065</t>
+  </si>
+  <si>
+    <t>0.0001,0.0108,0.9988,0.0002</t>
+  </si>
+  <si>
+    <t>0.9582,0.0169,0.0146,0.0059</t>
+  </si>
+  <si>
+    <t>0.0031,0.0159,0.9889,0.0005</t>
+  </si>
+  <si>
+    <t>0.0085,0.0267,0.9773,0.0015</t>
+  </si>
+  <si>
+    <t>0.0076,0.0046,0.9792,0.0059</t>
+  </si>
+  <si>
+    <t>0.0023,0.0510,0.9956,0.0003</t>
+  </si>
+  <si>
+    <t>0.0004,0.0015,0.9984,0.0001</t>
+  </si>
+  <si>
+    <t>0.0178,0.0023,0.9896,0.0002</t>
+  </si>
+  <si>
+    <t>0.0034,0.0079,0.9895,0.0014</t>
+  </si>
+  <si>
+    <t>0.1883,0.0131,0.8281,0.0093</t>
+  </si>
+  <si>
+    <t>0.0404,0.0031,0.9594,0.0044</t>
+  </si>
+  <si>
+    <t>0.0755,0.0257,0.9133,0.0028</t>
+  </si>
+  <si>
+    <t>0.0094,0.6352,0.6789,0.0013</t>
+  </si>
+  <si>
+    <t>0.1567,0.1265,0.7325,0.0028</t>
+  </si>
+  <si>
+    <t>0.4650,0.0404,0.4869,0.0022</t>
+  </si>
+  <si>
+    <t>0.9463,0.0032,0.0563,0.0048</t>
+  </si>
+  <si>
+    <t>0.1007,0.0319,0.8586,0.0053</t>
+  </si>
+  <si>
+    <t>0.4648,0.7253,0.0020,0.0014</t>
+  </si>
+  <si>
+    <t>0.0260,0.9831,0.0011,0.0004</t>
+  </si>
+  <si>
+    <t>0.8211,0.3092,0.0030,0.0004</t>
+  </si>
+  <si>
+    <t>0.9551,0.0523,0.0041,0.0017</t>
+  </si>
+  <si>
+    <t>0.3646,0.7531,0.0080,0.0018</t>
+  </si>
+  <si>
+    <t>0.5904,0.4007,0.0462,0.0144</t>
+  </si>
+  <si>
+    <t>0.9722,0.0019,0.0214,0.0019</t>
+  </si>
+  <si>
+    <t>0.9390,0.0073,0.0244,0.0143</t>
+  </si>
+  <si>
+    <t>0.8866,0.0074,0.1629,0.0026</t>
+  </si>
+  <si>
+    <t>0.8240,0.0317,0.1357,0.0204</t>
+  </si>
+  <si>
+    <t>0.0092,0.0021,0.9810,0.0058</t>
+  </si>
+  <si>
+    <t>0.0062,0.0736,0.9431,0.0109</t>
+  </si>
+  <si>
+    <t>0.0016,0.0112,0.9914,0.0017</t>
+  </si>
+  <si>
+    <t>0.0649,0.0874,0.8925,0.0072</t>
+  </si>
+  <si>
+    <t>0.0065,0.4654,0.7296,0.0107</t>
+  </si>
+  <si>
+    <t>0.9945,0.0014,0.0008,0.0015</t>
+  </si>
+  <si>
+    <t>0.9801,0.0110,0.0088,0.0026</t>
+  </si>
+  <si>
+    <t>0.9617,0.0315,0.0013,0.0042</t>
+  </si>
+  <si>
+    <t>0.8267,0.3037,0.0050,0.0046</t>
+  </si>
+  <si>
+    <t>0.9923,0.0021,0.0018,0.0015</t>
+  </si>
+  <si>
+    <t>0.9899,0.0070,0.0005,0.0009</t>
+  </si>
+  <si>
+    <t>0.9827,0.0033,0.0010,0.0060</t>
+  </si>
+  <si>
+    <t>0.9892,0.0027,0.0016,0.0026</t>
+  </si>
+  <si>
+    <t>0.0021,0.0131,0.9899,0.0032</t>
+  </si>
+  <si>
+    <t>0.0435,0.0244,0.9274,0.0126</t>
+  </si>
+  <si>
+    <t>0.8741,0.0026,0.1025,0.0093</t>
+  </si>
+  <si>
+    <t>0.0040,0.0005,0.9961,0.0002</t>
+  </si>
+  <si>
+    <t>0.0038,0.0038,0.9933,0.0004</t>
+  </si>
+  <si>
+    <t>0.0011,0.0729,0.9861,0.0007</t>
+  </si>
+  <si>
+    <t>0.0019,0.0019,0.9955,0.0010</t>
+  </si>
+  <si>
+    <t>0.0130,0.0088,0.9628,0.0120</t>
+  </si>
+  <si>
+    <t>0.0012,0.0106,0.9966,0.0005</t>
+  </si>
+  <si>
+    <t>0.0119,0.0183,0.9540,0.0135</t>
+  </si>
+  <si>
+    <t>0.0336,0.1638,0.8262,0.0037</t>
+  </si>
+  <si>
+    <t>0.9066,0.0056,0.1092,0.0058</t>
+  </si>
+  <si>
+    <t>0.9669,0.0006,0.0501,0.0006</t>
+  </si>
+  <si>
+    <t>0.9681,0.0096,0.0097,0.0020</t>
+  </si>
+  <si>
+    <t>0.9970,0.0016,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9796,0.0185,0.0014,0.0013</t>
+  </si>
+  <si>
+    <t>0.9881,0.0108,0.0017,0.0005</t>
+  </si>
+  <si>
+    <t>0.9944,0.0020,0.0011,0.0006</t>
+  </si>
+  <si>
+    <t>0.9962,0.0005,0.0001,0.0016</t>
+  </si>
+  <si>
+    <t>0.9846,0.0179,0.0016,0.0006</t>
+  </si>
+  <si>
+    <t>0.9966,0.0012,0.0008,0.0004</t>
+  </si>
+  <si>
+    <t>0.9939,0.0018,0.0010,0.0013</t>
+  </si>
+  <si>
+    <t>0.0204,0.0179,0.9647,0.0009</t>
+  </si>
+  <si>
+    <t>0.0005,0.0053,0.9977,0.0002</t>
+  </si>
+  <si>
+    <t>0.0105,0.0673,0.9339,0.0198</t>
+  </si>
+  <si>
+    <t>0.1143,0.0228,0.8803,0.0029</t>
+  </si>
+  <si>
+    <t>0.0004,0.0004,0.9978,0.0012</t>
+  </si>
+  <si>
+    <t>0.0266,0.1769,0.8125,0.1034</t>
+  </si>
+  <si>
+    <t>0.0177,0.0053,0.9655,0.0096</t>
+  </si>
+  <si>
+    <t>0.0044,0.0013,0.9715,0.0344</t>
+  </si>
+  <si>
+    <t>0.9426,0.0027,0.0009,0.0667</t>
+  </si>
+  <si>
+    <t>0.0097,0.0523,0.0014,0.9883</t>
+  </si>
+  <si>
+    <t>0.2823,0.0039,0.0015,0.8681</t>
+  </si>
+  <si>
+    <t>0.0039,0.0001,0.0008,0.9973</t>
+  </si>
+  <si>
+    <t>0.0021,0.0010,0.0016,0.9977</t>
+  </si>
+  <si>
+    <t>0.2007,0.0491,0.0006,0.7403</t>
   </si>
 </sst>
 </file>
@@ -1959,7 +1971,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1973,7 +1985,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1987,7 +1999,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2001,7 +2013,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2015,7 +2027,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2029,7 +2041,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2043,7 +2055,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2057,7 +2069,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2071,7 +2083,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2085,7 +2097,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2099,7 +2111,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2113,7 +2125,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2127,7 +2139,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2138,10 +2150,10 @@
         <v>261</v>
       </c>
       <c r="C15" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D15" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2155,7 +2167,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2169,7 +2181,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2183,7 +2195,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2197,7 +2209,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2211,7 +2223,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2225,7 +2237,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2239,7 +2251,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2253,7 +2265,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2264,10 +2276,10 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D24" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2281,7 +2293,7 @@
         <v>259</v>
       </c>
       <c r="D25" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2295,7 +2307,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2309,7 +2321,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2323,7 +2335,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2337,7 +2349,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2351,7 +2363,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2362,10 +2374,10 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D31" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2376,10 +2388,10 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D32" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2393,7 +2405,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2407,7 +2419,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2421,7 +2433,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2432,10 +2444,10 @@
         <v>259</v>
       </c>
       <c r="C36" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D36" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2446,10 +2458,10 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2463,7 +2475,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2477,7 +2489,7 @@
         <v>261</v>
       </c>
       <c r="D39" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2491,7 +2503,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2505,7 +2517,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2519,7 +2531,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2530,10 +2542,10 @@
         <v>263</v>
       </c>
       <c r="C43" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2547,7 +2559,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2561,7 +2573,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2572,10 +2584,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D46" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2589,7 +2601,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2603,7 +2615,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2617,7 +2629,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2631,7 +2643,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2645,7 +2657,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2659,7 +2671,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2673,7 +2685,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2687,7 +2699,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2701,7 +2713,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2715,7 +2727,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2729,7 +2741,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2743,7 +2755,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2757,7 +2769,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2771,7 +2783,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2785,7 +2797,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2799,7 +2811,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2813,7 +2825,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2827,7 +2839,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2841,7 +2853,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2855,7 +2867,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2869,7 +2881,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2883,7 +2895,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2897,7 +2909,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2911,7 +2923,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2922,10 +2934,10 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2939,7 +2951,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2953,7 +2965,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2967,7 +2979,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2981,7 +2993,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2992,10 +3004,10 @@
         <v>262</v>
       </c>
       <c r="C76" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D76" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3009,7 +3021,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3023,7 +3035,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3037,7 +3049,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3051,7 +3063,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3065,7 +3077,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3079,7 +3091,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3093,7 +3105,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3107,7 +3119,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3118,10 +3130,10 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3135,7 +3147,7 @@
         <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3146,10 +3158,10 @@
         <v>263</v>
       </c>
       <c r="C87" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D87" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3163,7 +3175,7 @@
         <v>262</v>
       </c>
       <c r="D88" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3177,7 +3189,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3191,7 +3203,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3205,7 +3217,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3219,7 +3231,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3233,7 +3245,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3247,7 +3259,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3261,7 +3273,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3275,7 +3287,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3289,7 +3301,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3303,7 +3315,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3317,7 +3329,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3331,7 +3343,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3345,7 +3357,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3359,7 +3371,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3373,7 +3385,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3387,7 +3399,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3401,7 +3413,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3415,7 +3427,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3429,7 +3441,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3443,7 +3455,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3457,7 +3469,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3471,7 +3483,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3485,7 +3497,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3499,7 +3511,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3513,7 +3525,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3527,7 +3539,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3538,10 +3550,10 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D115" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3555,7 +3567,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3566,10 +3578,10 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D117" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3580,10 +3592,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3594,10 +3606,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="D119" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3611,7 +3623,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3625,7 +3637,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3639,7 +3651,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3653,7 +3665,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3667,7 +3679,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3681,7 +3693,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3692,10 +3704,10 @@
         <v>259</v>
       </c>
       <c r="C126" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3709,7 +3721,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3723,7 +3735,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3737,7 +3749,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3751,7 +3763,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3765,7 +3777,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3779,7 +3791,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3793,7 +3805,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3807,7 +3819,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3821,7 +3833,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3835,7 +3847,7 @@
         <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3849,7 +3861,7 @@
         <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3863,7 +3875,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3877,7 +3889,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3891,7 +3903,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3902,10 +3914,10 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3919,7 +3931,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3933,7 +3945,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3947,7 +3959,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3961,7 +3973,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3975,7 +3987,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3989,7 +4001,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4003,7 +4015,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4017,7 +4029,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4031,7 +4043,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4045,7 +4057,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4059,7 +4071,7 @@
         <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4073,7 +4085,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4087,7 +4099,7 @@
         <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4101,7 +4113,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4112,10 +4124,10 @@
         <v>261</v>
       </c>
       <c r="C156" t="s">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="D156" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4129,7 +4141,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4143,7 +4155,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4154,10 +4166,10 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D159" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4171,7 +4183,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4185,7 +4197,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4199,7 +4211,7 @@
         <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4213,7 +4225,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4227,7 +4239,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4241,7 +4253,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4255,7 +4267,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4269,7 +4281,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4283,7 +4295,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4297,7 +4309,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4311,7 +4323,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4325,7 +4337,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4339,7 +4351,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4353,7 +4365,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4364,10 +4376,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4381,7 +4393,7 @@
         <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4392,10 +4404,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D176" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4409,7 +4421,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4423,7 +4435,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4437,7 +4449,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4451,7 +4463,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4465,7 +4477,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4479,7 +4491,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4493,7 +4505,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4507,7 +4519,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4521,7 +4533,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4535,7 +4547,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4549,7 +4561,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4563,7 +4575,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4577,7 +4589,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4591,7 +4603,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4605,7 +4617,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4619,7 +4631,7 @@
         <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4630,10 +4642,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D193" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4647,7 +4659,7 @@
         <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4658,10 +4670,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D195" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4675,7 +4687,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4689,7 +4701,7 @@
         <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4703,7 +4715,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4717,7 +4729,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4731,7 +4743,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4742,10 +4754,10 @@
         <v>259</v>
       </c>
       <c r="C201" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4759,7 +4771,7 @@
         <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4773,7 +4785,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4787,7 +4799,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4801,7 +4813,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4815,7 +4827,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4829,7 +4841,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4843,7 +4855,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4857,7 +4869,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4871,7 +4883,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4885,7 +4897,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4899,7 +4911,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4913,7 +4925,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4927,7 +4939,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4941,7 +4953,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4955,7 +4967,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4969,7 +4981,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4983,7 +4995,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4997,7 +5009,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5011,7 +5023,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5025,7 +5037,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5039,7 +5051,7 @@
         <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5053,7 +5065,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5067,7 +5079,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5081,7 +5093,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5095,7 +5107,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5109,7 +5121,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5123,7 +5135,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5137,7 +5149,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5151,7 +5163,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5165,7 +5177,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5179,7 +5191,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5193,7 +5205,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5207,7 +5219,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5221,7 +5233,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5235,7 +5247,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5249,7 +5261,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5263,7 +5275,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5277,7 +5289,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5291,7 +5303,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5305,7 +5317,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5319,7 +5331,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5333,7 +5345,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5347,7 +5359,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5361,7 +5373,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5375,7 +5387,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5389,7 +5401,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5403,7 +5415,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5417,7 +5429,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5431,7 +5443,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5445,7 +5457,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5459,7 +5471,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5473,7 +5485,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5487,7 +5499,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5501,7 +5513,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>518</v>
+        <v>522</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5515,7 +5527,7 @@
         <v>260</v>
       </c>
       <c r="D256" t="s">
-        <v>519</v>
+        <v>523</v>
       </c>
     </row>
   </sheetData>
